--- a/artfynd/A 24437-2026 artfynd.xlsx
+++ b/artfynd/A 24437-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130082674</v>
+        <v>130082359</v>
       </c>
       <c r="B2" t="n">
-        <v>58198</v>
+        <v>58388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>786807</v>
+        <v>786624</v>
       </c>
       <c r="R2" t="n">
-        <v>7251109</v>
+        <v>7251108</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>02:48</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>02:48</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,45 +783,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130082359</v>
+        <v>130081622</v>
       </c>
       <c r="B3" t="n">
-        <v>58258</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>786624</v>
+        <v>786777</v>
       </c>
       <c r="R3" t="n">
-        <v>7251108</v>
+        <v>7251098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>02:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>02:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130081622</v>
+        <v>130082674</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>786777</v>
+        <v>786807</v>
       </c>
       <c r="R4" t="n">
-        <v>7251098</v>
+        <v>7251109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>02:21</t>
+          <t>02:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>02:21</t>
+          <t>02:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130082360</v>
+        <v>130082675</v>
       </c>
       <c r="B5" t="n">
-        <v>58506</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,7 +1047,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>786552</v>
+        <v>786862</v>
       </c>
       <c r="R5" t="n">
-        <v>7251085</v>
+        <v>7251110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>02:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>02:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130082675</v>
+        <v>133647255</v>
       </c>
       <c r="B6" t="n">
-        <v>58198</v>
+        <v>58596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,43 +1145,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103041</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>786862</v>
+        <v>786495</v>
       </c>
       <c r="R6" t="n">
-        <v>7251110</v>
+        <v>7251021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>02:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>02:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,7 +1226,6 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1243,6 +1238,351 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133647632</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>786718</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7251065</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>02:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>02:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130082360</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>786552</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7251085</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130082672</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>786806</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7251140</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24437-2026 artfynd.xlsx
+++ b/artfynd/A 24437-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082359</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130081622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082674</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082675</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133647255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133647632</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082360</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,8 +1623,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082672</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>